--- a/data/trans_orig/P41C1_AOS_2023_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P41C1_AOS_2023_R-Provincia-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en años que han tardado en que algún miembro de la pareja se quede embarazada</t>
+          <t>Tiempo medio en años que han tardado en que algún miembro de la pareja se quede embarazada (tasa de respuesta: 93,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 10,89</t>
+          <t>0,82; 11,6</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,93</t>
+          <t>0,54; 4,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,06</t>
+          <t>1,46; 3,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,58</t>
+          <t>1,22; 3,4</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 12,03</t>
+          <t>1,07; 12,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 6,92</t>
+          <t>0,95; 6,98</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,11</t>
+          <t>2,15; 4,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,7</t>
+          <t>2,46; 5,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,53</t>
+          <t>2,58; 4,55</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,0</t>
+          <t>0,9; 3,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,29; 9,34</t>
+          <t>2,19; 8,66</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,6</t>
+          <t>1,93; 4,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,04</t>
+          <t>2,6; 5,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,31</t>
+          <t>2,47; 4,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41C1_AOS_2023_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P41C1_AOS_2023_R-Provincia-trans_orig.xlsx
@@ -553,12 +553,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,56</t>
+          <t>4,52</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,56</t>
+          <t>4,52</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>8,03</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>5,24</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 11,6</t>
+          <t>1,74; 11,54</t>
         </is>
       </c>
     </row>
@@ -653,12 +653,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>2,27</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>1,99</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,61</t>
+          <t>0,53; 4,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,93</t>
+          <t>1,33; 3,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,4</t>
+          <t>1,16; 3,23</t>
         </is>
       </c>
     </row>
@@ -703,12 +703,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,87</t>
+          <t>3,96</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,42</t>
+          <t>2,4</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 12,01</t>
+          <t>0,96; 11,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,98</t>
+          <t>0,97; 8,19</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>1,71</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,01</t>
+          <t>0,17; 2,94</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>3,59</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>3,59</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>3,01</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,73</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>3,49</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,18</t>
+          <t>2,26; 4,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,78</t>
+          <t>2,46; 5,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,55</t>
+          <t>2,68; 4,54</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>2,82</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6,48</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>4,02</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,76</t>
+          <t>0,9; 3,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 15,0</t>
+          <t>2,0; 15,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,19; 8,66</t>
+          <t>2,25; 8,48</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>2,93</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>3,39</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>3,17</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,76</t>
+          <t>2,03; 4,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,07</t>
+          <t>2,41; 4,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,29</t>
+          <t>2,5; 4,3</t>
         </is>
       </c>
     </row>
